--- a/part5testplan.xlsx
+++ b/part5testplan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14204dc00927b22a/Documents/GitHub/certCourseRepo/html^Mjava/JSAT2/part1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Desktop\HolmesDev\certCourseRepo\html+java\JSAT2\part5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{A65D925A-8171-4E22-8B08-62705AC897FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{411052AA-7BF4-451E-83AA-728B8CFC423B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8BE66F-1F6F-4B4D-BFC2-1D16CAD5EEE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="56">
   <si>
     <t>Test Case Description</t>
   </si>
@@ -99,67 +99,103 @@
     <t>open app in google</t>
   </si>
   <si>
-    <t>Check if the sequentialSearch() is working</t>
-  </si>
-  <si>
     <t>November 19th, 2025</t>
   </si>
   <si>
-    <t>use console.log(sequentialSearch(array, 14));</t>
-  </si>
-  <si>
-    <t>use console.log(sequentialSearch(array, 99));</t>
-  </si>
-  <si>
-    <t>use console.log(sequentialSearch(array, 19));</t>
-  </si>
-  <si>
-    <t>use console.log(sequentialSearch(array, 8));</t>
-  </si>
-  <si>
     <t>the app opened in google</t>
   </si>
   <si>
-    <t>returns with index 3 in console</t>
-  </si>
-  <si>
-    <t>returns with -1 in console</t>
-  </si>
-  <si>
-    <t>returns with index 5 in console</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
-    <t>Check if the binarySearch() is working</t>
-  </si>
-  <si>
-    <t>returns with index 8 in console</t>
-  </si>
-  <si>
-    <t>returns with index 1 in console</t>
-  </si>
-  <si>
-    <t>returns with index 9 in console</t>
-  </si>
-  <si>
-    <t>the console showed index 3</t>
-  </si>
-  <si>
-    <t>the console showed -1</t>
-  </si>
-  <si>
-    <t>the console showed index 5</t>
-  </si>
-  <si>
-    <t>the console showed index 8</t>
-  </si>
-  <si>
-    <t>the console showed index 1</t>
-  </si>
-  <si>
-    <t>the console showed index 9</t>
+    <t>use the search by id button to search for id 4</t>
+  </si>
+  <si>
+    <t>the movie of id 4 will show up in the movie list</t>
+  </si>
+  <si>
+    <t>the movie list showed the movie with the id of 4</t>
+  </si>
+  <si>
+    <t>November 28th, 2025</t>
+  </si>
+  <si>
+    <t>use the search by title button to search for "son of the mask"</t>
+  </si>
+  <si>
+    <t>the movie with the title "Son of the Mask" will show up in the movie list</t>
+  </si>
+  <si>
+    <t>the movie list showed the movie with the title of "Son of the mask"</t>
+  </si>
+  <si>
+    <t>check if the search section is working as well as the refresh list button</t>
+  </si>
+  <si>
+    <t>use the refresh list button</t>
+  </si>
+  <si>
+    <t>the movie list will refresh to its original state of showing all movies</t>
+  </si>
+  <si>
+    <t>the console showed its original state with all movies</t>
+  </si>
+  <si>
+    <t>check if the sort section is working</t>
+  </si>
+  <si>
+    <t>use the sort a-z button</t>
+  </si>
+  <si>
+    <t>the movie list will arrange all movies in alphabetical order</t>
+  </si>
+  <si>
+    <t>the movie list arranged all movies in alphabetical order</t>
+  </si>
+  <si>
+    <t>use the sort z-a button</t>
+  </si>
+  <si>
+    <t>the movie list will arrange all movies in reverse alphabetical order</t>
+  </si>
+  <si>
+    <t>the movie list arranged all movies in reverse alphabetical order</t>
+  </si>
+  <si>
+    <t>use the best movies button</t>
+  </si>
+  <si>
+    <t>the movie list will arrange all movies in order of highest to lowest rating</t>
+  </si>
+  <si>
+    <t>the movie list arranged all movies in order of highest to lowest rating</t>
+  </si>
+  <si>
+    <t>check if the add movie section is working</t>
+  </si>
+  <si>
+    <t>input an id, a title, a year, and a rating, and then use the submit button</t>
+  </si>
+  <si>
+    <t>a new movie with the information given will appear in the movie list</t>
+  </si>
+  <si>
+    <t>a new movie appeared in the movie list with all the information given</t>
+  </si>
+  <si>
+    <t>use the sort section buttons</t>
+  </si>
+  <si>
+    <t>the movie list will arrange all the movies including the new movie added</t>
+  </si>
+  <si>
+    <t>the movie list arranged all movies including the new movie added</t>
+  </si>
+  <si>
+    <t>the movie list will refresh to its default state, and the new movie added will be in there</t>
+  </si>
+  <si>
+    <t>the movie list refreshed to its default state and the new movie was in there</t>
   </si>
 </sst>
 </file>
@@ -542,7 +578,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -588,49 +624,98 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -640,7 +725,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -650,6 +734,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -695,15 +797,9 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -725,18 +821,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -752,50 +836,14 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1078,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883A4F42-1B46-4B1E-B91B-251F58B3FD09}">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:Z49"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1093,406 +1141,555 @@
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:26" ht="18.75" customHeight="1">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="13">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="23" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="24"/>
+      <c r="B2" s="25"/>
       <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="23" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="28"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="86" t="s">
+      <c r="I2" s="25"/>
+      <c r="J2" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="82" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="83"/>
-      <c r="F3" s="76" t="s">
+      <c r="E3" s="37"/>
+      <c r="F3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="76" t="s">
+      <c r="G3" s="40"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="78"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="87"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="81"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1">
+      <c r="J3" s="40"/>
+      <c r="K3" s="33"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="31"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="35"/>
+    </row>
+    <row r="5" spans="1:26" ht="18.75" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="73" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="18" t="s">
+      <c r="E5" s="18"/>
+      <c r="F5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="74"/>
-      <c r="K5" s="75"/>
-    </row>
-    <row r="6" spans="1:11" ht="36" customHeight="1">
+      <c r="J5" s="20"/>
+      <c r="K5" s="21"/>
+    </row>
+    <row r="6" spans="1:26" ht="36" customHeight="1">
       <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="18" t="s">
+      <c r="B6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="74"/>
-      <c r="K6" s="75"/>
-    </row>
-    <row r="7" spans="1:11" ht="34.5" customHeight="1">
+      <c r="J6" s="20"/>
+      <c r="K6" s="21"/>
+    </row>
+    <row r="7" spans="1:26" ht="47.25" customHeight="1">
       <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="73" t="s">
+      <c r="B7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="74"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="18" t="s">
+      <c r="E7" s="18"/>
+      <c r="F7" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="74"/>
-      <c r="K7" s="75"/>
-    </row>
-    <row r="8" spans="1:11" ht="32.25" customHeight="1">
+      <c r="J7" s="20"/>
+      <c r="K7" s="21"/>
+    </row>
+    <row r="8" spans="1:26" ht="48" customHeight="1">
       <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="73" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="74"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="18" t="s">
+      <c r="B8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="74"/>
-      <c r="K8" s="75"/>
-    </row>
-    <row r="9" spans="1:11" ht="31.7" customHeight="1">
-      <c r="A9" s="4">
-        <v>5</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" ht="6" customHeight="1"/>
-    <row r="11" spans="1:11" ht="18" customHeight="1">
-      <c r="A11" s="21" t="s">
+      <c r="J8" s="20"/>
+      <c r="K8" s="21"/>
+    </row>
+    <row r="9" spans="1:26" ht="31.7" customHeight="1">
+      <c r="P9" s="89"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="91"/>
+      <c r="V9" s="91"/>
+      <c r="W9" s="91"/>
+      <c r="X9" s="91"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="90"/>
+    </row>
+    <row r="10" spans="1:26" ht="24" customHeight="1"/>
+    <row r="11" spans="1:26" ht="18" customHeight="1">
+      <c r="A11" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="22"/>
+      <c r="B11" s="43"/>
       <c r="C11" s="13">
         <v>2</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="23" t="s">
+      <c r="E11" s="43"/>
+      <c r="F11" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="24"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="23" t="s">
+      <c r="E12" s="25"/>
+      <c r="F12" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="27"/>
+      <c r="H12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="24"/>
-      <c r="J12" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="28"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="86" t="s">
+      <c r="I12" s="25"/>
+      <c r="J12" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="29"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="78"/>
-      <c r="D13" s="82" t="s">
+      <c r="C13" s="33"/>
+      <c r="D13" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="83"/>
-      <c r="F13" s="76" t="s">
+      <c r="E13" s="37"/>
+      <c r="F13" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G13" s="77"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="76" t="s">
+      <c r="G13" s="40"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="77"/>
-      <c r="K13" s="78"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="87"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="81"/>
-    </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1">
+      <c r="J13" s="40"/>
+      <c r="K13" s="33"/>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="31"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="35"/>
+    </row>
+    <row r="15" spans="1:26" ht="18" customHeight="1">
       <c r="A15" s="4">
         <v>1</v>
       </c>
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="73" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="74"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="18" t="s">
+      <c r="E15" s="18"/>
+      <c r="F15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="74"/>
-      <c r="K15" s="75"/>
-    </row>
-    <row r="16" spans="1:11" ht="33" customHeight="1">
+      <c r="J15" s="20"/>
+      <c r="K15" s="21"/>
+    </row>
+    <row r="16" spans="1:26" ht="47.25" customHeight="1">
       <c r="A16" s="4">
         <v>2</v>
       </c>
-      <c r="B16" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="73" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="74"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="18" t="s">
+      <c r="B16" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="74"/>
-      <c r="K16" s="75"/>
-    </row>
-    <row r="17" spans="1:11" ht="33" customHeight="1">
+      <c r="J16" s="20"/>
+      <c r="K16" s="21"/>
+    </row>
+    <row r="17" spans="1:11" ht="50.25" customHeight="1">
       <c r="A17" s="4">
         <v>3</v>
       </c>
-      <c r="B17" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="73" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="18" t="s">
+      <c r="B17" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="74"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="18" t="s">
+      <c r="E17" s="18"/>
+      <c r="F17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="74"/>
-      <c r="K17" s="75"/>
-    </row>
-    <row r="18" spans="1:11" ht="33" customHeight="1">
+      <c r="J17" s="20"/>
+      <c r="K17" s="21"/>
+    </row>
+    <row r="18" spans="1:11" ht="48.75" customHeight="1">
       <c r="A18" s="4">
         <v>4</v>
       </c>
-      <c r="B18" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="74"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="18" t="s">
+      <c r="B18" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="74"/>
-      <c r="K18" s="75"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="21"/>
     </row>
     <row r="19" spans="1:11" ht="33" customHeight="1">
-      <c r="A19" s="4">
+      <c r="A19" s="89"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+    </row>
+    <row r="20" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A20" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="13">
+        <v>3</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="43"/>
+      <c r="F20" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+    </row>
+    <row r="21" spans="1:11" ht="68.099999999999994" hidden="1" customHeight="1">
+      <c r="A21" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="73" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="74"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="18" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="27"/>
+      <c r="H21" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="29"/>
+    </row>
+    <row r="22" spans="1:11" ht="50.1" customHeight="1">
+      <c r="A22" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="D22" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="37"/>
+      <c r="F22" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="40"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="40"/>
+      <c r="K22" s="33"/>
+    </row>
+    <row r="23" spans="1:11" ht="44.1" customHeight="1">
+      <c r="A23" s="31"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="35"/>
+    </row>
+    <row r="24" spans="1:11" ht="48.95" customHeight="1">
+      <c r="A24" s="4">
+        <v>1</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20" spans="1:11" ht="23.1" customHeight="1"/>
-    <row r="21" spans="1:11" ht="68.099999999999994" hidden="1" customHeight="1"/>
-    <row r="22" spans="1:11" ht="50.1" customHeight="1"/>
-    <row r="23" spans="1:11" ht="44.1" customHeight="1"/>
-    <row r="24" spans="1:11" ht="48.95" customHeight="1"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="21"/>
+    </row>
+    <row r="25" spans="1:11" ht="46.5" customHeight="1">
+      <c r="A25" s="4">
+        <v>2</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="20"/>
+      <c r="K25" s="21"/>
+    </row>
+    <row r="26" spans="1:11" ht="48" customHeight="1">
+      <c r="A26" s="4">
+        <v>3</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="20"/>
+      <c r="K26" s="21"/>
+    </row>
+    <row r="27" spans="1:11" ht="53.25" customHeight="1">
+      <c r="A27" s="4">
+        <v>4</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="20"/>
+      <c r="K27" s="21"/>
+    </row>
     <row r="29" spans="1:11">
       <c r="A29" s="5"/>
     </row>
@@ -1507,52 +1704,48 @@
     <row r="48" ht="36" customHeight="1"/>
     <row r="49" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="F11:K11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="I13:K14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
+  <mergeCells count="87">
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:E23"/>
+    <mergeCell ref="F22:H23"/>
+    <mergeCell ref="I22:K23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="D3:E4"/>
+    <mergeCell ref="F3:H4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:K20"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="I3:K4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
@@ -1562,18 +1755,43 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="D3:E4"/>
-    <mergeCell ref="F3:H4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="F13:H14"/>
+    <mergeCell ref="I13:K14"/>
+    <mergeCell ref="F11:K11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:K18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -1599,25 +1817,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="14">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2"/>
@@ -1633,125 +1851,125 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="31.5">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="23" t="s">
+      <c r="G3" s="27"/>
+      <c r="H3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="28"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="29" t="s">
+      <c r="E5" s="50"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" ht="54" customHeight="1">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="36.950000000000003" customHeight="1">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="38"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="54"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="20" spans="1:1" ht="23.1" customHeight="1"/>
     <row r="21" spans="1:1" ht="68.099999999999994" hidden="1" customHeight="1"/>
@@ -1773,6 +1991,19 @@
     <row r="49" ht="36" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="I5:K6"/>
     <mergeCell ref="I8:K8"/>
@@ -1789,19 +2020,6 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="F5:H6"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1818,24 +2036,24 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.95" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="52"/>
+      <c r="B1" s="74"/>
       <c r="C1" s="15">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
       <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11" ht="15.75">
@@ -1852,29 +2070,29 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="58"/>
+      <c r="B3" s="78"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="58"/>
-      <c r="F3" s="60" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="61"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="81"/>
+      <c r="H3" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="58"/>
-      <c r="J3" s="62" t="s">
+      <c r="I3" s="78"/>
+      <c r="J3" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="63"/>
+      <c r="K3" s="83"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
       <c r="A4" s="5"/>
@@ -1890,119 +2108,103 @@
       <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="18.95" customHeight="1">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="45" t="s">
+      <c r="C5" s="64"/>
+      <c r="D5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="41" t="s">
+      <c r="E5" s="68"/>
+      <c r="F5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="49"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="41" t="s">
+      <c r="G5" s="71"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="42"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="40"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="44"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:11" ht="63.95" customHeight="1">
       <c r="A7" s="7">
         <v>1</v>
       </c>
-      <c r="B7" s="54"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="56"/>
-      <c r="D7" s="54"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="56"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="66"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="59"/>
     </row>
     <row r="8" spans="1:11" ht="48" customHeight="1">
       <c r="A8" s="8">
         <v>2</v>
       </c>
-      <c r="B8" s="54"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="56"/>
-      <c r="D8" s="54"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="56"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="66"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="59"/>
     </row>
     <row r="9" spans="1:11" ht="48" customHeight="1">
       <c r="A9" s="8">
         <v>3</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="56"/>
-      <c r="D9" s="54"/>
+      <c r="D9" s="55"/>
       <c r="E9" s="56"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="66"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="59"/>
     </row>
     <row r="10" spans="1:11" ht="63.95" customHeight="1">
       <c r="A10" s="11">
         <v>4</v>
       </c>
-      <c r="B10" s="54"/>
+      <c r="B10" s="55"/>
       <c r="C10" s="56"/>
-      <c r="D10" s="54"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="56"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="65"/>
-      <c r="K10" s="66"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:C6"/>
     <mergeCell ref="D5:E6"/>
@@ -2016,6 +2218,22 @@
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="I5:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2030,25 +2248,25 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="14">
         <v>3</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:14" ht="15.75">
       <c r="A2" s="2"/>
@@ -2064,29 +2282,29 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="15.75">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="23" t="s">
+      <c r="G3" s="27"/>
+      <c r="H3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="28"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:14" ht="15.75">
       <c r="A4" s="1"/>
@@ -2102,178 +2320,149 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="29" t="s">
+      <c r="E5" s="50"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:14" ht="69" customHeight="1">
       <c r="A7" s="12">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="18"/>
       <c r="N8" s="9"/>
     </row>
     <row r="9" spans="1:14" ht="38.1" customHeight="1">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:14" ht="35.1" customHeight="1">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:14" ht="36" customHeight="1">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="18"/>
     </row>
     <row r="12" spans="1:14" ht="84.95" customHeight="1">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:14" ht="30.95" customHeight="1">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="20"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="I5:K6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:K10"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:H13"/>
@@ -2286,6 +2475,35 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="I12:K12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="I5:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2300,24 +2518,24 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="2" spans="1:11" ht="15.95" customHeight="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="52"/>
+      <c r="B2" s="74"/>
       <c r="C2" s="15">
         <v>4</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="54" t="s">
+      <c r="E2" s="74"/>
+      <c r="F2" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
       <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
@@ -2334,29 +2552,29 @@
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="58"/>
+      <c r="B4" s="78"/>
       <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="60" t="s">
+      <c r="E4" s="78"/>
+      <c r="F4" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="61"/>
-      <c r="H4" s="59" t="s">
+      <c r="G4" s="81"/>
+      <c r="H4" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="58"/>
-      <c r="J4" s="62" t="s">
+      <c r="I4" s="78"/>
+      <c r="J4" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="63"/>
+      <c r="K4" s="83"/>
     </row>
     <row r="5" spans="1:11" ht="15.75">
       <c r="A5" s="5"/>
@@ -2375,72 +2593,88 @@
       <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="70" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="68" t="s">
+      <c r="E6" s="87"/>
+      <c r="F6" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="72"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="68" t="s">
+      <c r="G6" s="88"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="72"/>
-      <c r="K6" s="69"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="85"/>
     </row>
     <row r="7" spans="1:11" ht="63.95" customHeight="1">
       <c r="A7" s="7">
         <v>1</v>
       </c>
-      <c r="B7" s="54"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="56"/>
-      <c r="D7" s="54"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="56"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="66"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="59"/>
     </row>
     <row r="8" spans="1:11" ht="48" customHeight="1">
       <c r="A8" s="8">
         <v>2</v>
       </c>
-      <c r="B8" s="54"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="56"/>
-      <c r="D8" s="54"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="56"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="66"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="59"/>
     </row>
     <row r="9" spans="1:11" ht="48" customHeight="1">
       <c r="A9" s="8">
         <v>3</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="55"/>
       <c r="C9" s="56"/>
-      <c r="D9" s="54"/>
+      <c r="D9" s="55"/>
       <c r="E9" s="56"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="66"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:H8"/>
@@ -2449,22 +2683,6 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2479,25 +2697,25 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="14">
         <v>1</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15.75">
       <c r="A2" s="2"/>
@@ -2513,29 +2731,29 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="23" t="s">
+      <c r="G3" s="27"/>
+      <c r="H3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="28"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
       <c r="A4" s="1"/>
@@ -2551,100 +2769,100 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="29" t="s">
+      <c r="E5" s="50"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" ht="66.95" customHeight="1">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="35.1" customHeight="1">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:11" ht="38.1" customHeight="1">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:11" ht="45.95" customHeight="1">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="13" spans="1:11" ht="15.75">
       <c r="A13" s="1"/>
@@ -2701,6 +2919,27 @@
     <row r="49" ht="36.950000000000003" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="I5:K6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:H10"/>
@@ -2709,11 +2948,195 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="I5:K6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;11&amp;K000000 OFFICIAL</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C3CF33-D8DB-124A-8B0F-8D298481330E}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.75">
+      <c r="A1" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="14">
+        <v>2</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75">
+      <c r="A3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="27"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="29"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="50"/>
+      <c r="F5" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+    </row>
+    <row r="7" spans="1:11" ht="66" customHeight="1">
+      <c r="A7" s="4">
+        <v>1</v>
+      </c>
+      <c r="B7" s="23"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" spans="1:11" ht="53.1" customHeight="1">
+      <c r="A8" s="4">
+        <v>2</v>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:11" ht="39" customHeight="1">
+      <c r="A9" s="4">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" ht="75.95" customHeight="1">
+      <c r="A10" s="4">
+        <v>4</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:H7"/>
@@ -2722,6 +3145,11 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="I5:K6"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:K1"/>
@@ -2738,31 +3166,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C3CF33-D8DB-124A-8B0F-8D298481330E}">
-  <dimension ref="A1:K10"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9A716-8B7D-874D-A8BA-B87A8DBCF69D}">
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="14">
-        <v>2</v>
-      </c>
-      <c r="D1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15.75">
       <c r="A2" s="2"/>
@@ -2778,27 +3206,29 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="28"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="25"/>
+      <c r="J3" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
       <c r="A4" s="1"/>
@@ -2814,389 +3244,148 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="29" t="s">
+      <c r="E5" s="50"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-    </row>
-    <row r="7" spans="1:11" ht="66" customHeight="1">
-      <c r="A7" s="4">
-        <v>1</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
-    </row>
-    <row r="8" spans="1:11" ht="53.1" customHeight="1">
-      <c r="A8" s="4">
-        <v>2</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
-    </row>
-    <row r="9" spans="1:11" ht="39" customHeight="1">
-      <c r="A9" s="4">
-        <v>3</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" ht="75.95" customHeight="1">
-      <c r="A10" s="4">
-        <v>4</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
-    </row>
-  </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="I5:K6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:K10"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;11&amp;K000000 OFFICIAL</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9A716-8B7D-874D-A8BA-B87A8DBCF69D}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
-  <sheetData>
-    <row r="1" spans="1:11" ht="15.75">
-      <c r="A1" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="14">
-        <v>3</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.75">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75">
-      <c r="A3" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="28"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" ht="63" customHeight="1">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="51.95" customHeight="1">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:11" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:11" ht="51.95" customHeight="1">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:11" ht="51.95" customHeight="1">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="18"/>
     </row>
     <row r="12" spans="1:11" ht="78.95" customHeight="1">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:11" ht="63" customHeight="1">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="20"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="I5:K6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:K10"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:H13"/>
@@ -3209,6 +3398,35 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="I12:K12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="I5:K6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -3223,25 +3441,25 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="43"/>
       <c r="C1" s="13">
         <v>4</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="F1" s="16" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="15.75">
       <c r="A2" s="2"/>
@@ -3257,29 +3475,29 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="23" t="s">
+      <c r="G3" s="27"/>
+      <c r="H3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="27" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="28"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
       <c r="A4" s="1"/>
@@ -3295,88 +3513,100 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="29" t="s">
+      <c r="E5" s="50"/>
+      <c r="F5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="29" t="s">
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" spans="1:11" ht="18.95" customHeight="1">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" ht="62.1" customHeight="1">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="57.95" customHeight="1">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="73"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:11" ht="48.95" customHeight="1">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:H6"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:H9"/>
@@ -3390,18 +3620,6 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:H6"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
